--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,20 +489,16 @@
           <t>2026-09-20 06:57:04</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
+      <c r="D2" t="n">
+        <v>4500011739</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -541,6 +537,303 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:45:07</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:45:07</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:16:26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:16:26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:16:26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>100</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2179,7 +2179,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21 11:14:14</t>
+          <t>2026-09-21 11:45:21</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2195,41 +2195,41 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>316.8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>09 Agustus 2026</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>30 Aug 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>250000</v>
+        <v>25000</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026 </t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2241,13 +2241,21 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21 11:45:21</t>
+          <t>2026-09-21 12:58:42</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2255,24 +2263,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>316.8</v>
+        <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2281,23 +2289,23 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>09 Agustus 2026</t>
+          <t>19 September 2026</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>19 September 2026</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>25000</v>
+        <v>5054500</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2311,19 +2319,19 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>19 September 2026</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>18 September 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21 12:58:42</t>
+          <t>2026-09-22 10:55:02</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2331,49 +2339,49 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19 September 2026</t>
+          <t>09 Agustus 2026</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>19 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>5054500</v>
+        <v>25000000</v>
       </c>
       <c r="L28" t="n">
         <v>100</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2387,12 +2395,12 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>19 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>18 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2428,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2442,14 +2450,14 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>25000000</v>
+        <v>17500000</v>
       </c>
       <c r="L29" t="n">
         <v>100</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2491,16 +2499,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2518,14 +2526,14 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="L30" t="n">
         <v>100</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2601,7 +2609,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2648,7 +2656,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2670,14 +2678,14 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L32" t="n">
         <v>100</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2779,7 +2787,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:02</t>
+          <t>2026-09-22 11:26:05</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2787,49 +2795,49 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4500011739</v>
+        <v>4500011586</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>09 Agustus 2026</t>
+          <t>16 Agustus 2026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>16 Agustus 2026</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>15000000</v>
+        <v>21000000</v>
       </c>
       <c r="L34" t="n">
         <v>100</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2843,7 +2851,7 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>05 Agustus 2026</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -2855,7 +2863,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-22 11:26:05</t>
+          <t>2026-09-28 11:26:31</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2863,49 +2871,49 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4500011586</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>16 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>21000000</v>
+        <v>25000</v>
       </c>
       <c r="L35" t="n">
         <v>100</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2919,12 +2927,12 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
-          <t>05 Agustus 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>07 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -2934,20 +2942,16 @@
           <t>2026-09-28 11:26:31</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B36" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D36" t="n">
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2960,7 +2964,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2969,12 +2973,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2985,7 +2989,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3014,20 +3018,16 @@
           <t>2026-09-28 11:26:31</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B37" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D37" t="n">
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -3094,20 +3094,16 @@
           <t>2026-09-28 11:26:31</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B38" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D38" t="n">
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3174,20 +3170,16 @@
           <t>2026-09-28 11:26:31</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B39" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D39" t="n">
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3204,7 +3196,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3225,7 +3217,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3254,20 +3246,16 @@
           <t>2026-09-28 11:26:31</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B40" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D40" t="n">
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3284,7 +3272,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3305,7 +3293,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3334,20 +3322,16 @@
           <t>2026-09-28 11:26:31</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B41" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D41" t="n">
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3360,7 +3344,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3374,7 +3358,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3385,7 +3369,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3411,40 +3395,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-28 11:26:31</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-09-30 12:23:54</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4500011739</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3454,18 +3434,18 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>30 Agustus 2026</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>25000</v>
+        <v>250000</v>
       </c>
       <c r="L42" t="n">
         <v>100</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3479,12 +3459,812 @@
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>30 Agustus 2026</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>07 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Aqua 600 ml</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>240</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>7500</v>
+      </c>
+      <c r="L43" t="n">
+        <v>100</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>24</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L44" t="n">
+        <v>100</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>24</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L45" t="n">
+        <v>100</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>48</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L46" t="n">
+        <v>100</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>48</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>84500</v>
+      </c>
+      <c r="L47" t="n">
+        <v>100</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Coca Cola</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>48</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L48" t="n">
+        <v>100</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fanta</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>48</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L49" t="n">
+        <v>100</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>48</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L50" t="n">
+        <v>100</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>48</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L51" t="n">
+        <v>100</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:23:37</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>48</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L52" t="n">
+        <v>100</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X52"/>
+  <dimension ref="A1:X53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,20 +3474,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B43" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D43" t="n">
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3554,20 +3550,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B44" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D44" t="n">
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3634,20 +3626,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B45" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D45" t="n">
+        <v>0</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3714,20 +3702,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B46" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D46" t="n">
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3794,20 +3778,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B47" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D47" t="n">
+        <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3874,20 +3854,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B48" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D48" t="n">
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3954,20 +3930,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B49" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D49" t="n">
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -4034,20 +4006,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B50" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D50" t="n">
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -4114,20 +4082,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B51" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D51" t="n">
+        <v>0</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -4194,20 +4158,16 @@
           <t>2026-09-30 13:23:37</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B52" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D52" t="n">
+        <v>0</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -4268,6 +4228,86 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:43:01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/X/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>07 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>10 September 2026</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>131650000</v>
+      </c>
+      <c r="L53" t="n">
+        <v>100</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>02 Oktober 2026</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>03 Oktober 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X53"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4234,20 +4234,16 @@
           <t>2026-10-01 13:43:01</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B53" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D53" t="n">
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -4308,6 +4304,162 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:15:26</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>036/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4500011739</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>07 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>10 September 2026</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L54" t="n">
+        <v>100</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>10 September 2026</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:38:36</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>07 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>46750000</v>
+      </c>
+      <c r="L55" t="n">
+        <v>100</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3471,7 +3471,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
+          <t>2026-10-01 13:43:01</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -3487,41 +3487,41 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>07 Agustus 2026</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>10 September 2026</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>7500</v>
+        <v>131650000</v>
       </c>
       <c r="L43" t="n">
         <v>100</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3535,19 +3535,19 @@
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>02 Oktober 2026</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Oktober 2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
+          <t>2026-10-02 09:15:26</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3555,49 +3555,49 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>24</v>
+        <v>489.8</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>07 Agustus 2026</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>10 September 2026</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>19500</v>
+        <v>25000</v>
       </c>
       <c r="L44" t="n">
         <v>100</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3611,19 +3611,19 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>10 September 2026</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
+          <t>2026-10-02 09:38:36</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -3631,49 +3631,51 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>07 Agustus 2026</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>15600</v>
+        <v>46750000</v>
       </c>
       <c r="L45" t="n">
         <v>100</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3687,31 +3689,35 @@
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3720,11 +3726,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3742,7 +3748,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>13000</v>
+        <v>32500</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -3775,19 +3781,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>0</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3800,7 +3810,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3851,19 +3861,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3872,11 +3886,11 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coca Cola</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3894,7 +3908,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9750</v>
+        <v>26000</v>
       </c>
       <c r="L48" t="n">
         <v>100</v>
@@ -3927,19 +3941,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>0</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3948,15 +3966,15 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fanta</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4003,19 +4021,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -4024,15 +4046,15 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4046,7 +4068,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L50" t="n">
         <v>100</v>
@@ -4079,19 +4101,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>0</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -4100,29 +4126,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="L51" t="n">
         <v>100</v>
@@ -4155,19 +4181,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-30 13:23:37</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>0</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -4180,7 +4210,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4189,12 +4219,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -4231,32 +4261,36 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-01 13:43:01</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4265,23 +4299,23 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>07 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>10 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>131650000</v>
+        <v>19500</v>
       </c>
       <c r="L53" t="n">
         <v>100</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4295,69 +4329,73 @@
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
-          <t>02 Oktober 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>03 Oktober 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-02 09:15:26</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>7201250141</v>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4500011739</v>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>489.8</v>
+        <v>36</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>07 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>10 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>25000</v>
+        <v>32500</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4371,19 +4409,19 @@
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
-          <t>10 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:36</t>
+          <t>2026-10-03 06:53:29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4393,26 +4431,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4421,23 +4459,23 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>07 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>46750000</v>
+        <v>32500</v>
       </c>
       <c r="L55" t="n">
         <v>100</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4451,12 +4489,172 @@
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>36</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>03 Oktober 2026</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>03 Oktober 2026</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L56" t="n">
+        <v>100</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:53:29</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>72</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L57" t="n">
+        <v>100</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X69"/>
+  <dimension ref="A1:X79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4640,10 +4640,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B58" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4720,10 +4718,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B59" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -4800,10 +4796,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B60" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4880,10 +4874,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B61" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4960,10 +4952,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B62" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -5040,10 +5030,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B63" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -5120,10 +5108,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B64" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5200,10 +5186,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B65" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -5280,10 +5264,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B66" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -5360,10 +5342,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B67" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -5440,10 +5420,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B68" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -5520,10 +5498,8 @@
           <t>2026-10-03 12:00:00</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B69" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -5594,6 +5570,796 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:05</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>16</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L70" t="n">
+        <v>100</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:05</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L71" t="n">
+        <v>100</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:05</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L72" t="n">
+        <v>100</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:05</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L73" t="n">
+        <v>100</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:54:05</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="L74" t="n">
+        <v>100</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:03:48</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L75" t="n">
+        <v>100</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:03:48</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L76" t="n">
+        <v>100</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:03:48</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L77" t="n">
+        <v>100</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:03:48</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>105</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L78" t="n">
+        <v>100</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:03:48</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="L79" t="n">
+        <v>100</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>04 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X79"/>
+  <dimension ref="A1:X102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2255,7 +2255,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21 12:58:42</t>
+          <t>2026-09-22 10:55:02</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2263,49 +2263,49 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19 September 2026</t>
+          <t>09 Agustus 2026</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>5054500</v>
+        <v>25000000</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2319,12 +2319,12 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>19 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>18 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2374,14 +2374,14 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>25000000</v>
+        <v>17500000</v>
       </c>
       <c r="L28" t="n">
         <v>100</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2423,16 +2423,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2450,14 +2450,14 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="L29" t="n">
         <v>100</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2602,14 +2602,14 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L31" t="n">
         <v>100</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2711,7 +2711,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-22 10:55:02</t>
+          <t>2026-09-22 11:26:05</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2719,49 +2719,49 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4500011739</v>
+        <v>4500011586</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>09 Agustus 2026</t>
+          <t>16 Agustus 2026</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>16 Agustus 2026</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>15000000</v>
+        <v>21000000</v>
       </c>
       <c r="L33" t="n">
         <v>100</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2775,7 +2775,7 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>05 Agustus 2026</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -2787,7 +2787,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-22 11:26:05</t>
+          <t>2026-09-28 11:26:31</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2795,49 +2795,49 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4500011586</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>21000000</v>
+        <v>25000</v>
       </c>
       <c r="L34" t="n">
         <v>100</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2851,12 +2851,12 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>05 Agustus 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>07 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-28 11:26:31</t>
+          <t>2026-09-30 12:23:54</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3327,28 +3327,28 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3358,18 +3358,18 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>30 Agustus 2026</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>25000</v>
+        <v>250000</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3383,19 +3383,19 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>30 Agustus 2026</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>07 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-30 12:23:54</t>
+          <t>2026-10-01 13:43:01</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -3403,49 +3403,49 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4500011739</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>07 Agustus 2026</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>30 Agustus 2026</t>
+          <t>10 September 2026</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>250000</v>
+        <v>131650000</v>
       </c>
       <c r="L42" t="n">
         <v>100</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3459,19 +3459,19 @@
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>30 Agustus 2026</t>
+          <t>02 Oktober 2026</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 Oktober 2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01 13:43:01</t>
+          <t>2026-10-02 09:15:26</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -3479,28 +3479,28 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>4500011739</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>489.8</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3514,14 +3514,14 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>131650000</v>
+        <v>25000</v>
       </c>
       <c r="L43" t="n">
         <v>100</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3535,19 +3535,19 @@
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>02 Oktober 2026</t>
+          <t>10 September 2026</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>03 Oktober 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-02 09:15:26</t>
+          <t>2026-10-02 09:38:36</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3555,28 +3555,30 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>4500011739</v>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>489.8</v>
+        <v>1</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3586,18 +3588,18 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>10 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>25000</v>
+        <v>46750000</v>
       </c>
       <c r="L44" t="n">
         <v>100</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3611,19 +3613,19 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>10 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:36</t>
+          <t>2026-10-03 09:24:05</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -3631,51 +3633,51 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>07 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>46750000</v>
+        <v>32500</v>
       </c>
       <c r="L45" t="n">
         <v>100</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3689,12 +3691,12 @@
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3726,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3746,7 +3748,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>32500</v>
+        <v>84500</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -3802,11 +3804,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3824,7 +3826,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>84500</v>
+        <v>26000</v>
       </c>
       <c r="L47" t="n">
         <v>100</v>
@@ -3880,11 +3882,11 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3902,7 +3904,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>26000</v>
+        <v>9750</v>
       </c>
       <c r="L48" t="n">
         <v>100</v>
@@ -3958,11 +3960,11 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3980,7 +3982,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L49" t="n">
         <v>100</v>
@@ -4036,11 +4038,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4058,7 +4060,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="L50" t="n">
         <v>100</v>
@@ -4114,7 +4116,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -4122,7 +4124,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4136,7 +4138,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>13000</v>
+        <v>9750</v>
       </c>
       <c r="L51" t="n">
         <v>100</v>
@@ -4192,7 +4194,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -4214,7 +4216,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L52" t="n">
         <v>100</v>
@@ -4270,11 +4272,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4292,7 +4294,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>19500</v>
+        <v>32500</v>
       </c>
       <c r="L53" t="n">
         <v>100</v>
@@ -4348,7 +4350,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -4426,7 +4428,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -4439,12 +4441,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Oktober 2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Oktober 2026</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -4504,11 +4506,11 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4517,16 +4519,16 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>03 Oktober 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>03 Oktober 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>32500</v>
+        <v>15600</v>
       </c>
       <c r="L56" t="n">
         <v>100</v>
@@ -4559,7 +4561,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 12:00:00</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -4567,7 +4569,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4582,36 +4584,36 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="L57" t="n">
         <v>100</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4625,12 +4627,12 @@
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
@@ -4660,11 +4662,11 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4682,7 +4684,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>32500</v>
+        <v>84500</v>
       </c>
       <c r="L58" t="n">
         <v>100</v>
@@ -4738,11 +4740,11 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4760,7 +4762,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>84500</v>
+        <v>26000</v>
       </c>
       <c r="L59" t="n">
         <v>100</v>
@@ -4816,11 +4818,11 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4838,7 +4840,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>26000</v>
+        <v>9750</v>
       </c>
       <c r="L60" t="n">
         <v>100</v>
@@ -4894,11 +4896,11 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4916,7 +4918,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
@@ -4972,11 +4974,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4994,7 +4996,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="L62" t="n">
         <v>100</v>
@@ -5050,7 +5052,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -5072,7 +5074,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>13000</v>
+        <v>9750</v>
       </c>
       <c r="L63" t="n">
         <v>100</v>
@@ -5128,7 +5130,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -5150,7 +5152,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="L64" t="n">
         <v>100</v>
@@ -5206,11 +5208,11 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -5228,7 +5230,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>19500</v>
+        <v>15600</v>
       </c>
       <c r="L65" t="n">
         <v>100</v>
@@ -5284,11 +5286,11 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5306,7 +5308,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="L66" t="n">
         <v>100</v>
@@ -5362,7 +5364,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -5440,7 +5442,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -5495,7 +5497,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-03 12:54:05</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -5503,51 +5505,51 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>32500</v>
+        <v>200000</v>
       </c>
       <c r="L69" t="n">
         <v>100</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -5561,12 +5563,12 @@
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
     </row>
@@ -5596,15 +5598,15 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5614,18 +5616,18 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="L70" t="n">
         <v>100</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -5669,12 +5671,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -5682,7 +5684,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5696,14 +5698,14 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="L71" t="n">
         <v>100</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -5747,20 +5749,20 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5770,18 +5772,18 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>1600000</v>
+        <v>350000</v>
       </c>
       <c r="L72" t="n">
         <v>100</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -5825,25 +5827,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5852,14 +5854,14 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>350000</v>
+        <v>3250000</v>
       </c>
       <c r="L73" t="n">
         <v>100</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -5885,7 +5887,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:05</t>
+          <t>2026-10-03 13:03:48</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -5893,7 +5895,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5903,12 +5905,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -5916,28 +5918,28 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>3250000</v>
+        <v>1600000</v>
       </c>
       <c r="L74" t="n">
         <v>100</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -5951,12 +5953,12 @@
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
@@ -5966,10 +5968,8 @@
           <t>2026-10-03 13:03:48</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B75" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6010,14 +6010,14 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="L75" t="n">
         <v>100</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -6046,10 +6046,8 @@
           <t>2026-10-03 13:03:48</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B76" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6063,20 +6061,20 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6086,18 +6084,18 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="L76" t="n">
         <v>100</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -6126,10 +6124,8 @@
           <t>2026-10-03 13:03:48</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B77" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6143,20 +6139,20 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6170,14 +6166,14 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="L77" t="n">
         <v>100</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -6206,10 +6202,8 @@
           <t>2026-10-03 13:03:48</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B78" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6223,25 +6217,25 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6250,14 +6244,14 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>200000</v>
+        <v>3250000</v>
       </c>
       <c r="L78" t="n">
         <v>100</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -6283,22 +6277,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:48</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6308,36 +6300,36 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>3250000</v>
+        <v>32500</v>
       </c>
       <c r="L79" t="n">
         <v>100</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -6351,12 +6343,1830 @@
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>6</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>84500</v>
+      </c>
+      <c r="L80" t="n">
+        <v>100</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L81" t="n">
+        <v>100</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>72</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L82" t="n">
+        <v>100</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>10</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L83" t="n">
+        <v>100</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>72</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L84" t="n">
+        <v>100</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>72</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L85" t="n">
+        <v>100</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>72</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L86" t="n">
+        <v>100</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>48</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L87" t="n">
+        <v>100</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>10</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L88" t="n">
+        <v>100</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>10</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L89" t="n">
+        <v>100</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:22</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>10</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L90" t="n">
+        <v>100</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>5</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L91" t="n">
+        <v>100</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>6</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>84500</v>
+      </c>
+      <c r="L92" t="n">
+        <v>100</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>5</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L93" t="n">
+        <v>100</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>72</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L94" t="n">
+        <v>100</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>10</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L95" t="n">
+        <v>100</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>72</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L96" t="n">
+        <v>100</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>72</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>9750</v>
+      </c>
+      <c r="L97" t="n">
+        <v>100</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>72</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L98" t="n">
+        <v>100</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>48</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L99" t="n">
+        <v>100</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>10</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L100" t="n">
+        <v>100</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>10</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L101" t="n">
+        <v>100</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:44:21</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>10</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L102" t="n">
+        <v>100</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X102"/>
+  <dimension ref="A1:X121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7216,10 +7216,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B91" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7296,10 +7294,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B92" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7376,10 +7372,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B93" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7456,10 +7450,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B94" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7536,10 +7528,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B95" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7616,10 +7606,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B96" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7696,10 +7684,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B97" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7776,10 +7762,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B98" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -7856,10 +7840,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B99" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -7936,10 +7918,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B100" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -8016,10 +7996,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B101" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -8096,10 +8074,8 @@
           <t>2026-10-05 09:44:21</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B102" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -8170,6 +8146,1498 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:50:09</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, main course</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>3195</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L103" t="n">
+        <v>100</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:50:09</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1486.5</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L104" t="n">
+        <v>100</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:07:08</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>040/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>30</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L105" t="n">
+        <v>100</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:34:17</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>30</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L106" t="n">
+        <v>100</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:34:17</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L107" t="n">
+        <v>100</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:34:17</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L108" t="n">
+        <v>100</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:50</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>30</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L109" t="n">
+        <v>100</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:50</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>750000</v>
+      </c>
+      <c r="L110" t="n">
+        <v>100</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:50</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>30</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>650000</v>
+      </c>
+      <c r="L111" t="n">
+        <v>100</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:50</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>650000</v>
+      </c>
+      <c r="L112" t="n">
+        <v>100</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:50</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L113" t="n">
+        <v>100</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18:50</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>30</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L114" t="n">
+        <v>100</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:41:07</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>30</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L115" t="n">
+        <v>100</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:33:47</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>48</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>04 September 2026</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>11 September 2026</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L116" t="n">
+        <v>100</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>11 September 2026</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:55</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>30</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L117" t="n">
+        <v>100</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:55</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>30</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L118" t="n">
+        <v>100</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:55</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>4</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>27 September 2026</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L119" t="n">
+        <v>100</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:55</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L120" t="n">
+        <v>100</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:55</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>30</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L121" t="n">
+        <v>100</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X121"/>
+  <dimension ref="A1:X125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9244,10 +9244,8 @@
           <t>2026-10-06 13:23:55</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B117" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -9324,10 +9322,8 @@
           <t>2026-10-06 13:23:55</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B118" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -9404,10 +9400,8 @@
           <t>2026-10-06 13:23:55</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B119" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -9484,10 +9478,8 @@
           <t>2026-10-06 13:23:55</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B120" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -9564,10 +9556,8 @@
           <t>2026-10-06 13:23:55</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B121" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -9638,6 +9628,320 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:52:52</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>048/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Laundry services</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>458.4</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L122" t="n">
+        <v>100</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:51:53</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Aqua 600 ml</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>2188</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>7500</v>
+      </c>
+      <c r="L123" t="n">
+        <v>100</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:51:53</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Aqua Galon Segel</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>15</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>53300</v>
+      </c>
+      <c r="L124" t="n">
+        <v>100</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:04:22</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>050/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L125" t="n">
+        <v>100</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X125"/>
+  <dimension ref="A1:X131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9868,10 +9868,8 @@
           <t>2026-10-06 19:04:22</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B125" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -9942,6 +9940,486 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:16</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L126" t="n">
+        <v>100</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:16</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="L127" t="n">
+        <v>100</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:16</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L128" t="n">
+        <v>100</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:16</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L129" t="n">
+        <v>100</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:16</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L130" t="n">
+        <v>100</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:11:16</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L131" t="n">
+        <v>100</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X131"/>
+  <dimension ref="A1:X145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9946,10 +9946,8 @@
           <t>2026-10-07 06:11:16</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B126" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -10026,10 +10024,8 @@
           <t>2026-10-07 06:11:16</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B127" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -10106,10 +10102,8 @@
           <t>2026-10-07 06:11:16</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B128" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -10186,10 +10180,8 @@
           <t>2026-10-07 06:11:16</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B129" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -10266,10 +10258,8 @@
           <t>2026-10-07 06:11:16</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B130" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -10346,10 +10336,8 @@
           <t>2026-10-07 06:11:16</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B131" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -10420,6 +10408,1108 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:41:55</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="L132" t="n">
+        <v>100</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:41:55</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="L133" t="n">
+        <v>100</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:00:04</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L134" t="n">
+        <v>100</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:00:04</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L135" t="n">
+        <v>100</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:22</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="L136" t="n">
+        <v>100</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>29 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:22</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="L137" t="n">
+        <v>100</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>29 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:22</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="L138" t="n">
+        <v>100</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>29 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:22</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="L139" t="n">
+        <v>100</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>29 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:32:22</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="L140" t="n">
+        <v>100</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>29 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:03</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="L141" t="n">
+        <v>100</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:03</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="L142" t="n">
+        <v>100</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:03</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="L143" t="n">
+        <v>100</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:03</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L144" t="n">
+        <v>100</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:41:03</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="L145" t="n">
+        <v>100</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X145"/>
+  <dimension ref="A1:X148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8149,7 +8149,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-06 09:50:09</t>
+          <t>2026-10-06 10:07:08</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8167,20 +8167,20 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8194,14 +8194,14 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>65000</v>
+        <v>750000</v>
       </c>
       <c r="L103" t="n">
         <v>100</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -8227,7 +8227,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-06 09:50:09</t>
+          <t>2026-10-06 10:34:17</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8245,20 +8245,20 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1486.5</v>
+        <v>30</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8272,14 +8272,14 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>33000</v>
+        <v>500000</v>
       </c>
       <c r="L104" t="n">
         <v>100</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -8305,7 +8305,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-06 10:07:08</t>
+          <t>2026-10-06 10:34:17</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -8350,14 +8350,14 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="L105" t="n">
         <v>100</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -8461,7 +8461,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:17</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -8506,14 +8506,14 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="L107" t="n">
         <v>100</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
+          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:17</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -8584,14 +8584,14 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="L108" t="n">
         <v>100</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
+          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -8662,14 +8662,14 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="L109" t="n">
         <v>100</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -8740,14 +8740,14 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="L110" t="n">
         <v>100</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -8818,14 +8818,14 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="L111" t="n">
         <v>100</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -8896,14 +8896,14 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="L112" t="n">
         <v>100</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -8929,7 +8929,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-06 11:41:07</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -8974,14 +8974,14 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="L113" t="n">
         <v>100</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -9007,7 +9007,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-06 12:33:47</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9030,36 +9030,36 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>11 September 2026</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>600000</v>
+        <v>250000</v>
       </c>
       <c r="L114" t="n">
         <v>100</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>11 September 2026</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-06 11:41:07</t>
+          <t>2026-10-06 13:23:55</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -9130,14 +9130,14 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>500000</v>
+        <v>1600000</v>
       </c>
       <c r="L115" t="n">
         <v>100</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -9163,7 +9163,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33:47</t>
+          <t>2026-10-06 13:23:55</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9181,41 +9181,41 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>11 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="L116" t="n">
         <v>100</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -9229,7 +9229,7 @@
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr">
         <is>
-          <t>11 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -9420,11 +9420,11 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>27 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -9475,7 +9475,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23:55</t>
+          <t>2026-10-06 17:52:52</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9493,20 +9493,20 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -9520,14 +9520,14 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="L120" t="n">
         <v>100</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -9553,7 +9553,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23:55</t>
+          <t>2026-10-06 18:51:53</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -9561,30 +9561,30 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>30</v>
+        <v>2188</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9598,14 +9598,14 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="L121" t="n">
         <v>100</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -9624,14 +9624,14 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-06 17:52:52</t>
+          <t>2026-10-06 18:51:53</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -9639,30 +9639,30 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>458.4</v>
+        <v>15</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9676,14 +9676,14 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>25000</v>
+        <v>53300</v>
       </c>
       <c r="L122" t="n">
         <v>100</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -9702,14 +9702,14 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-06 18:51:53</t>
+          <t>2026-10-06 19:04:22</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9727,20 +9727,20 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9754,14 +9754,14 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>7500</v>
+        <v>60000000</v>
       </c>
       <c r="L123" t="n">
         <v>100</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-06 18:51:53</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -9795,30 +9795,30 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9832,14 +9832,14 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>53300</v>
+        <v>25000000</v>
       </c>
       <c r="L124" t="n">
         <v>100</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -9858,14 +9858,14 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-06 19:04:22</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -9873,22 +9873,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9910,14 +9910,14 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>60000000</v>
+        <v>17500000</v>
       </c>
       <c r="L125" t="n">
         <v>100</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -9988,14 +9988,14 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>25000000</v>
+        <v>60000000</v>
       </c>
       <c r="L126" t="n">
         <v>100</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -10066,14 +10066,14 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="L127" t="n">
         <v>100</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -10144,14 +10144,14 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L128" t="n">
         <v>100</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L129" t="n">
         <v>100</v>
@@ -10255,7 +10255,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-07 08:41:55</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -10286,28 +10286,28 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>15000000</v>
+        <v>7500000</v>
       </c>
       <c r="L130" t="n">
         <v>100</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -10321,19 +10321,19 @@
       <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-07 08:41:55</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -10364,28 +10364,28 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>15000000</v>
+        <v>7500000</v>
       </c>
       <c r="L131" t="n">
         <v>100</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -10399,19 +10399,19 @@
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-07 08:41:55</t>
+          <t>2026-10-07 09:00:04</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -10419,22 +10419,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -10456,14 +10456,14 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="L132" t="n">
         <v>100</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -10489,7 +10489,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-07 08:41:55</t>
+          <t>2026-10-07 09:00:04</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -10497,22 +10497,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -10534,14 +10534,14 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="L133" t="n">
         <v>100</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -10567,7 +10567,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:04</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -10603,23 +10603,23 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="L134" t="n">
         <v>100</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -10633,7 +10633,7 @@
       <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
@@ -10645,7 +10645,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:04</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -10681,23 +10681,23 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="L135" t="n">
         <v>100</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -10711,7 +10711,7 @@
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -10768,14 +10768,14 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="L136" t="n">
         <v>100</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -10846,14 +10846,14 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="L137" t="n">
         <v>100</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -10957,7 +10957,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -10993,23 +10993,23 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="L139" t="n">
         <v>100</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -11023,7 +11023,7 @@
       <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
@@ -11035,7 +11035,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -11066,28 +11066,28 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="L140" t="n">
         <v>100</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -11101,7 +11101,7 @@
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
@@ -11116,10 +11116,8 @@
           <t>2026-10-07 10:41:03</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B141" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -11138,7 +11136,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -11160,14 +11158,14 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="L141" t="n">
         <v>100</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -11196,10 +11194,8 @@
           <t>2026-10-07 10:41:03</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B142" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -11213,12 +11209,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -11240,14 +11236,14 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="L142" t="n">
         <v>100</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -11276,10 +11272,8 @@
           <t>2026-10-07 10:41:03</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B143" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -11293,12 +11287,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -11306,7 +11300,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -11320,14 +11314,14 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="L143" t="n">
         <v>100</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -11353,17 +11347,15 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-07 11:27:18</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11391,12 +11383,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K144" t="n">
@@ -11407,7 +11399,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -11421,7 +11413,7 @@
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
@@ -11433,17 +11425,15 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-07 11:27:18</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -11466,17 +11456,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -11487,7 +11477,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -11501,12 +11491,250 @@
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
           <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:27:18</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>29 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>29 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>5520000</v>
+      </c>
+      <c r="L146" t="n">
+        <v>100</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>29 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:57:36</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, main course</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>3195</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L147" t="n">
+        <v>100</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:57:36</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1488</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L148" t="n">
+        <v>100</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -9085,7 +9085,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23:55</t>
+          <t>2026-10-06 17:52:52</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9103,20 +9103,20 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -9130,14 +9130,14 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="L115" t="n">
         <v>100</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -9163,7 +9163,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23:55</t>
+          <t>2026-10-06 18:51:53</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -9171,30 +9171,30 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>30</v>
+        <v>2188</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -9208,14 +9208,14 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="L116" t="n">
         <v>100</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -9234,14 +9234,14 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23:55</t>
+          <t>2026-10-06 18:51:53</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -9249,35 +9249,35 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>27 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9286,14 +9286,14 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>1600000</v>
+        <v>53300</v>
       </c>
       <c r="L117" t="n">
         <v>100</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -9312,14 +9312,14 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23:55</t>
+          <t>2026-10-06 19:04:22</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -9327,30 +9327,30 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -9364,14 +9364,14 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>1600000</v>
+        <v>60000000</v>
       </c>
       <c r="L118" t="n">
         <v>100</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -9390,14 +9390,14 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23:55</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9415,20 +9415,20 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -9442,14 +9442,14 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>1600000</v>
+        <v>25000000</v>
       </c>
       <c r="L119" t="n">
         <v>100</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -9475,7 +9475,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-06 17:52:52</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9498,15 +9498,15 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>458.4</v>
+        <v>1</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -9520,14 +9520,14 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="L120" t="n">
         <v>100</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -9553,7 +9553,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-06 18:51:53</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -9561,30 +9561,30 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9598,14 +9598,14 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>7500</v>
+        <v>60000000</v>
       </c>
       <c r="L121" t="n">
         <v>100</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -9624,14 +9624,14 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-06 18:51:53</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -9639,30 +9639,30 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9676,14 +9676,14 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>53300</v>
+        <v>60000000</v>
       </c>
       <c r="L122" t="n">
         <v>100</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -9702,14 +9702,14 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-06 19:04:22</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -9717,22 +9717,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9754,14 +9754,14 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="L123" t="n">
         <v>100</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -9832,14 +9832,14 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>25000000</v>
+        <v>15000000</v>
       </c>
       <c r="L124" t="n">
         <v>100</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-07 08:41:55</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -9896,28 +9896,28 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>17500000</v>
+        <v>7500000</v>
       </c>
       <c r="L125" t="n">
         <v>100</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -9931,19 +9931,19 @@
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-07 08:41:55</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -9974,28 +9974,28 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>60000000</v>
+        <v>7500000</v>
       </c>
       <c r="L126" t="n">
         <v>100</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -10009,19 +10009,19 @@
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-07 09:00:04</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -10029,22 +10029,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -10052,28 +10052,28 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>60000000</v>
+        <v>7600000</v>
       </c>
       <c r="L127" t="n">
         <v>100</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -10087,19 +10087,19 @@
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-07 09:00:04</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -10107,22 +10107,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -10130,28 +10130,28 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>15000000</v>
+        <v>7600000</v>
       </c>
       <c r="L128" t="n">
         <v>100</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -10165,19 +10165,19 @@
       <c r="V128" t="inlineStr"/>
       <c r="W128" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -10185,22 +10185,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -10208,28 +10208,28 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>15000000</v>
+        <v>5290000</v>
       </c>
       <c r="L129" t="n">
         <v>100</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -10243,19 +10243,19 @@
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-07 08:41:55</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -10263,22 +10263,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -10291,23 +10291,23 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>7500000</v>
+        <v>5290000</v>
       </c>
       <c r="L130" t="n">
         <v>100</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -10321,7 +10321,7 @@
       <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-07 08:41:55</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -10341,22 +10341,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -10369,23 +10369,23 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>7500000</v>
+        <v>6555000</v>
       </c>
       <c r="L131" t="n">
         <v>100</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -10399,7 +10399,7 @@
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -10411,7 +10411,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:04</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -10447,23 +10447,23 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>7600000</v>
+        <v>6555000</v>
       </c>
       <c r="L132" t="n">
         <v>100</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -10477,7 +10477,7 @@
       <c r="V132" t="inlineStr"/>
       <c r="W132" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
@@ -10489,7 +10489,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:04</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -10520,28 +10520,28 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>7600000</v>
+        <v>6555000</v>
       </c>
       <c r="L133" t="n">
         <v>100</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
       <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -10567,7 +10567,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K134" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -10633,7 +10633,7 @@
       <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
@@ -10645,7 +10645,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -10711,7 +10711,7 @@
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
@@ -10723,7 +10723,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -10789,7 +10789,7 @@
       <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X136" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -10837,23 +10837,23 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="L137" t="n">
         <v>100</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -10867,7 +10867,7 @@
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -10879,7 +10879,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -10915,23 +10915,23 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K138" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="L138" t="n">
         <v>100</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -10945,7 +10945,7 @@
       <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
@@ -10957,7 +10957,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-07 11:27:18</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10975,12 +10975,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -10993,23 +10993,23 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="L139" t="n">
         <v>100</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -11023,7 +11023,7 @@
       <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
@@ -11035,7 +11035,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-07 11:27:18</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -11071,23 +11071,23 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="L140" t="n">
         <v>100</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -11101,7 +11101,7 @@
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-07 11:27:18</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -11149,23 +11149,23 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>6555000</v>
+        <v>5520000</v>
       </c>
       <c r="L141" t="n">
         <v>100</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -11179,7 +11179,7 @@
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
@@ -11191,7 +11191,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-07 11:57:36</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -11214,36 +11214,36 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>3195</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>7600000</v>
+        <v>65000</v>
       </c>
       <c r="L142" t="n">
         <v>100</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -11257,19 +11257,19 @@
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-07 11:57:36</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -11292,11 +11292,11 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>1488</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -11305,23 +11305,23 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>7600000</v>
+        <v>33000</v>
       </c>
       <c r="L143" t="n">
         <v>100</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -11335,71 +11335,73 @@
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:18</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:57:15</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>7600000</v>
+        <v>1600000</v>
       </c>
       <c r="L144" t="n">
         <v>100</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -11413,71 +11415,73 @@
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:18</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:57:15</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>7600000</v>
+        <v>1600000</v>
       </c>
       <c r="L145" t="n">
         <v>100</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -11491,71 +11495,73 @@
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:18</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>7201250141</v>
+          <t>2026-10-10 08:57:15</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K146" t="n">
-        <v>5520000</v>
+        <v>1600000</v>
       </c>
       <c r="L146" t="n">
         <v>100</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -11569,19 +11575,19 @@
       <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-07 11:57:36</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11591,7 +11597,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -11601,20 +11607,20 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11628,14 +11634,14 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>65000</v>
+        <v>1600000</v>
       </c>
       <c r="L147" t="n">
         <v>100</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -11661,7 +11667,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-07 11:57:36</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11671,7 +11677,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -11681,20 +11687,20 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1488</v>
+        <v>30</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11708,14 +11714,14 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>33000</v>
+        <v>1600000</v>
       </c>
       <c r="L148" t="n">
         <v>100</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X148"/>
+  <dimension ref="A1:X150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11350,10 +11350,8 @@
           <t>2026-10-10 08:57:15</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B144" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -11430,10 +11428,8 @@
           <t>2026-10-10 08:57:15</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B145" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -11510,10 +11506,8 @@
           <t>2026-10-10 08:57:15</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B146" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -11590,10 +11584,8 @@
           <t>2026-10-10 08:57:15</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B147" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -11670,10 +11662,8 @@
           <t>2026-10-10 08:57:15</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B148" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -11744,6 +11734,164 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:26:58</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="L149" t="n">
+        <v>100</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:35:35</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>052/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>15 September 2026</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>15 September 2026</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="L150" t="n">
+        <v>100</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>15 September 2026</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>15 September 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X150"/>
+  <dimension ref="A1:X154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11818,10 +11818,8 @@
           <t>2026-10-13 10:35:35</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B150" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -11892,6 +11890,322 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:23:53</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>4500011794</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>50</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>30 Januari 2026</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>30 Januari 2026</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L151" t="n">
+        <v>100</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>30 Januari 2026</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>30 Januari 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:23:53</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>4500011794</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>50</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>30 Januari 2026</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>30 Januari 2026</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L152" t="n">
+        <v>100</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>30 Januari 2026</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>30 Januari 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:53:42</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>4500011795</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>04 September 2026</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>04 September 2026</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>175000</v>
+      </c>
+      <c r="L153" t="n">
+        <v>100</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>04 September 2026</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:53:42</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>4500011795</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>04 September 2026</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>04 September 2026</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L154" t="n">
+        <v>100</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>04 September 2026</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X154"/>
+  <dimension ref="A1:X156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11191,7 +11191,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-07 11:57:36</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -11209,20 +11209,20 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -11236,14 +11236,14 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>65000</v>
+        <v>1600000</v>
       </c>
       <c r="L142" t="n">
         <v>100</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -11269,7 +11269,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-07 11:57:36</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -11287,20 +11287,20 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1488</v>
+        <v>30</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -11314,14 +11314,14 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>33000</v>
+        <v>1600000</v>
       </c>
       <c r="L143" t="n">
         <v>100</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -11526,11 +11526,11 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>27 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:15</t>
+          <t>2026-10-13 10:26:58</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -11589,51 +11589,51 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>1600000</v>
+        <v>1500000</v>
       </c>
       <c r="L147" t="n">
         <v>100</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -11647,19 +11647,19 @@
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:15</t>
+          <t>2026-10-13 10:35:35</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -11667,51 +11667,51 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>1600000</v>
+        <v>7500000</v>
       </c>
       <c r="L148" t="n">
         <v>100</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -11725,19 +11725,19 @@
       <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-13 10:26:58</t>
+          <t>2026-10-14 13:23:53</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -11745,12 +11745,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -11764,32 +11764,32 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>1500000</v>
+        <v>10000</v>
       </c>
       <c r="L149" t="n">
         <v>100</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -11803,19 +11803,19 @@
       <c r="V149" t="inlineStr"/>
       <c r="W149" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-13 10:35:35</t>
+          <t>2026-10-14 13:23:53</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -11842,32 +11842,32 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>7500000</v>
+        <v>15000</v>
       </c>
       <c r="L150" t="n">
         <v>100</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -11881,19 +11881,19 @@
       <c r="V150" t="inlineStr"/>
       <c r="W150" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-14 13:23:53</t>
+          <t>2026-10-14 13:53:42</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -11901,12 +11901,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -11920,32 +11920,32 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>10000</v>
+        <v>175000</v>
       </c>
       <c r="L151" t="n">
         <v>100</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -11959,19 +11959,19 @@
       <c r="V151" t="inlineStr"/>
       <c r="W151" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-10-14 13:23:53</t>
+          <t>2026-10-14 13:53:42</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -11979,12 +11979,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -11998,32 +11998,32 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K152" t="n">
-        <v>15000</v>
+        <v>100000</v>
       </c>
       <c r="L152" t="n">
         <v>100</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -12037,73 +12037,71 @@
       <c r="V152" t="inlineStr"/>
       <c r="W152" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-10-14 13:53:42</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-15 17:38:09</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>2</v>
+        <v>2578</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>175000</v>
+        <v>65000</v>
       </c>
       <c r="L153" t="n">
         <v>100</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -12117,73 +12115,71 @@
       <c r="V153" t="inlineStr"/>
       <c r="W153" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-10-14 13:53:42</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+          <t>2026-10-15 17:38:09</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Operational side consumption</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>1157</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K154" t="n">
-        <v>100000</v>
+        <v>33000</v>
       </c>
       <c r="L154" t="n">
         <v>100</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -12197,12 +12193,172 @@
       <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
         <is>
+          <t>03 Agustus 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:44:44</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>operational consumption</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>3195</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
           <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L155" t="n">
+        <v>100</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:44:44</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Operational side consumption</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1488</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L156" t="n">
+        <v>100</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_rincian_pekerjaan_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X156"/>
+  <dimension ref="A1:X155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3625,7 +3625,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 12:54:05</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -3633,51 +3633,51 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>32500</v>
+        <v>200000</v>
       </c>
       <c r="L45" t="n">
         <v>100</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3691,19 +3691,19 @@
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 12:54:05</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3711,51 +3711,51 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>84500</v>
+        <v>250000</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3769,19 +3769,19 @@
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 12:54:05</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3789,51 +3789,51 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>26000</v>
+        <v>1600000</v>
       </c>
       <c r="L47" t="n">
         <v>100</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3847,19 +3847,19 @@
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 12:54:05</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3867,51 +3867,51 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9750</v>
+        <v>350000</v>
       </c>
       <c r="L48" t="n">
         <v>100</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3925,19 +3925,19 @@
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 12:54:05</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3960,36 +3960,36 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>19500</v>
+        <v>3250000</v>
       </c>
       <c r="L49" t="n">
         <v>100</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -4003,19 +4003,19 @@
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>20 Mei 2026</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>18 Mei 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:03:48</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -4023,51 +4023,51 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>13000</v>
+        <v>1600000</v>
       </c>
       <c r="L50" t="n">
         <v>100</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -4081,19 +4081,19 @@
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:03:48</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -4101,51 +4101,51 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9750</v>
+        <v>250000</v>
       </c>
       <c r="L51" t="n">
         <v>100</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -4159,19 +4159,19 @@
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:03:48</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -4179,51 +4179,51 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>19500</v>
+        <v>350000</v>
       </c>
       <c r="L52" t="n">
         <v>100</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4237,19 +4237,19 @@
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:03:48</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -4257,51 +4257,51 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>32500</v>
+        <v>200000</v>
       </c>
       <c r="L53" t="n">
         <v>100</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4315,19 +4315,19 @@
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:03:48</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4350,36 +4350,36 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>32500</v>
+        <v>3250000</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4393,19 +4393,19 @@
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 Agustus 2026</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-06 10:07:08</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -4413,51 +4413,51 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>03 Oktober 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>03 Oktober 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>32500</v>
+        <v>750000</v>
       </c>
       <c r="L55" t="n">
         <v>100</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4471,19 +4471,19 @@
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-06 10:34:17</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -4491,51 +4491,51 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>15600</v>
+        <v>500000</v>
       </c>
       <c r="L56" t="n">
         <v>100</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4549,19 +4549,19 @@
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 10:34:17</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -4569,51 +4569,51 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>32500</v>
+        <v>500000</v>
       </c>
       <c r="L57" t="n">
         <v>100</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -4639,7 +4639,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 10:34:17</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -4647,51 +4647,51 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>84500</v>
+        <v>500000</v>
       </c>
       <c r="L58" t="n">
         <v>100</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4705,7 +4705,7 @@
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -4725,51 +4725,51 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>26000</v>
+        <v>750000</v>
       </c>
       <c r="L59" t="n">
         <v>100</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4783,7 +4783,7 @@
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -4803,51 +4803,51 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>9750</v>
+        <v>750000</v>
       </c>
       <c r="L60" t="n">
         <v>100</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -4861,7 +4861,7 @@
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -4881,51 +4881,51 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>19500</v>
+        <v>650000</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4939,7 +4939,7 @@
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -4959,51 +4959,51 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>13000</v>
+        <v>650000</v>
       </c>
       <c r="L62" t="n">
         <v>100</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -5017,7 +5017,7 @@
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -5037,51 +5037,51 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>9750</v>
+        <v>600000</v>
       </c>
       <c r="L63" t="n">
         <v>100</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -5095,7 +5095,7 @@
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -5107,7 +5107,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 11:18:50</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -5115,51 +5115,51 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>19500</v>
+        <v>600000</v>
       </c>
       <c r="L64" t="n">
         <v>100</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5173,7 +5173,7 @@
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 11:41:07</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -5193,51 +5193,51 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>15600</v>
+        <v>500000</v>
       </c>
       <c r="L65" t="n">
         <v>100</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -5251,7 +5251,7 @@
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -5263,7 +5263,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 12:33:47</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -5271,30 +5271,30 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5304,18 +5304,18 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>11 September 2026</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>32500</v>
+        <v>250000</v>
       </c>
       <c r="L66" t="n">
         <v>100</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>11 September 2026</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -5341,7 +5341,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 17:52:52</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -5349,51 +5349,51 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>10</v>
+        <v>458.4</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>32500</v>
+        <v>25000</v>
       </c>
       <c r="L67" t="n">
         <v>100</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -5407,7 +5407,7 @@
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -5419,7 +5419,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-06 18:51:53</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5442,11 +5442,11 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>10</v>
+        <v>2188</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5455,23 +5455,23 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>32500</v>
+        <v>7500</v>
       </c>
       <c r="L68" t="n">
         <v>100</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -5485,19 +5485,19 @@
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:05</t>
+          <t>2026-10-06 18:51:53</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5515,41 +5515,41 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>200000</v>
+        <v>53300</v>
       </c>
       <c r="L69" t="n">
         <v>100</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -5563,19 +5563,19 @@
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:05</t>
+          <t>2026-10-06 19:04:22</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -5606,28 +5606,28 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>250000</v>
+        <v>60000000</v>
       </c>
       <c r="L70" t="n">
         <v>100</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -5641,19 +5641,19 @@
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:05</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -5661,22 +5661,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -5684,28 +5684,28 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1600000</v>
+        <v>25000000</v>
       </c>
       <c r="L71" t="n">
         <v>100</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -5719,19 +5719,19 @@
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:05</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -5739,51 +5739,51 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>350000</v>
+        <v>17500000</v>
       </c>
       <c r="L72" t="n">
         <v>100</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -5797,19 +5797,19 @@
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-03 12:54:05</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -5840,28 +5840,28 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>3250000</v>
+        <v>60000000</v>
       </c>
       <c r="L73" t="n">
         <v>100</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -5875,19 +5875,19 @@
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
-          <t>20 Mei 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>18 Mei 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:48</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -5895,22 +5895,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -5918,28 +5918,28 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1600000</v>
+        <v>60000000</v>
       </c>
       <c r="L74" t="n">
         <v>100</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -5953,19 +5953,19 @@
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:48</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -5973,22 +5973,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -5996,28 +5996,28 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>250000</v>
+        <v>15000000</v>
       </c>
       <c r="L75" t="n">
         <v>100</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -6031,19 +6031,19 @@
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:48</t>
+          <t>2026-10-07 06:11:16</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -6051,51 +6051,51 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>350000</v>
+        <v>15000000</v>
       </c>
       <c r="L76" t="n">
         <v>100</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -6109,19 +6109,19 @@
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:48</t>
+          <t>2026-10-07 09:00:04</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6139,41 +6139,41 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>200000</v>
+        <v>7600000</v>
       </c>
       <c r="L77" t="n">
         <v>100</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -6187,7 +6187,7 @@
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -6199,7 +6199,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:48</t>
+          <t>2026-10-07 09:00:04</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -6235,23 +6235,23 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>3250000</v>
+        <v>7600000</v>
       </c>
       <c r="L78" t="n">
         <v>100</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -6265,7 +6265,7 @@
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
-          <t>04 Agustus 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -6285,51 +6285,51 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>32500</v>
+        <v>5290000</v>
       </c>
       <c r="L79" t="n">
         <v>100</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -6343,19 +6343,19 @@
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -6363,51 +6363,51 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>84500</v>
+        <v>5290000</v>
       </c>
       <c r="L80" t="n">
         <v>100</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -6421,19 +6421,19 @@
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -6441,51 +6441,51 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>26000</v>
+        <v>6555000</v>
       </c>
       <c r="L81" t="n">
         <v>100</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -6499,19 +6499,19 @@
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -6519,51 +6519,51 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>9750</v>
+        <v>6555000</v>
       </c>
       <c r="L82" t="n">
         <v>100</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -6577,19 +6577,19 @@
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 09:32:22</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -6597,51 +6597,51 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>19500</v>
+        <v>6555000</v>
       </c>
       <c r="L83" t="n">
         <v>100</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -6655,19 +6655,19 @@
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -6675,51 +6675,51 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>13000</v>
+        <v>5290000</v>
       </c>
       <c r="L84" t="n">
         <v>100</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -6733,19 +6733,19 @@
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -6753,51 +6753,51 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>9750</v>
+        <v>5290000</v>
       </c>
       <c r="L85" t="n">
         <v>100</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -6811,19 +6811,19 @@
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -6831,51 +6831,51 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>19500</v>
+        <v>6555000</v>
       </c>
       <c r="L86" t="n">
         <v>100</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -6889,19 +6889,19 @@
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -6909,51 +6909,51 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>15600</v>
+        <v>7600000</v>
       </c>
       <c r="L87" t="n">
         <v>100</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -6967,19 +6967,19 @@
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 10:41:03</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -6987,51 +6987,51 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>32500</v>
+        <v>7600000</v>
       </c>
       <c r="L88" t="n">
         <v>100</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -7045,19 +7045,19 @@
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>20 Agustus 2026</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 11:27:18</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -7065,51 +7065,51 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>32500</v>
+        <v>7600000</v>
       </c>
       <c r="L89" t="n">
         <v>100</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -7123,19 +7123,19 @@
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:22</t>
+          <t>2026-10-07 11:27:18</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -7143,51 +7143,51 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>23 Agustus 2026</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>32500</v>
+        <v>7600000</v>
       </c>
       <c r="L90" t="n">
         <v>100</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -7201,19 +7201,19 @@
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-07 11:27:18</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -7221,51 +7221,51 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>32500</v>
+        <v>5520000</v>
       </c>
       <c r="L91" t="n">
         <v>100</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -7279,19 +7279,19 @@
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>29 Agustus 2026</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -7299,51 +7299,51 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>84500</v>
+        <v>1600000</v>
       </c>
       <c r="L92" t="n">
         <v>100</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -7357,19 +7357,19 @@
       <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -7377,51 +7377,51 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>26000</v>
+        <v>1600000</v>
       </c>
       <c r="L93" t="n">
         <v>100</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -7435,19 +7435,19 @@
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -7455,51 +7455,51 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>9750</v>
+        <v>1600000</v>
       </c>
       <c r="L94" t="n">
         <v>100</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -7513,19 +7513,19 @@
       <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -7533,51 +7533,51 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>19500</v>
+        <v>1600000</v>
       </c>
       <c r="L95" t="n">
         <v>100</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -7591,19 +7591,19 @@
       <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-10 08:57:15</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -7611,51 +7611,51 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>13000</v>
+        <v>1600000</v>
       </c>
       <c r="L96" t="n">
         <v>100</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -7669,19 +7669,19 @@
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-13 10:26:58</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -7689,51 +7689,51 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>9750</v>
+        <v>1500000</v>
       </c>
       <c r="L97" t="n">
         <v>100</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -7747,19 +7747,19 @@
       <c r="V97" t="inlineStr"/>
       <c r="W97" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>14 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-13 10:35:35</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -7767,51 +7767,51 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>19500</v>
+        <v>7500000</v>
       </c>
       <c r="L98" t="n">
         <v>100</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -7825,19 +7825,19 @@
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-14 13:23:53</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -7845,51 +7845,51 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>15600</v>
+        <v>10000</v>
       </c>
       <c r="L99" t="n">
         <v>100</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -7903,19 +7903,19 @@
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-14 13:23:53</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -7923,51 +7923,51 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>32500</v>
+        <v>15000</v>
       </c>
       <c r="L100" t="n">
         <v>100</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -7981,19 +7981,19 @@
       <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>30 Januari 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-14 13:53:42</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -8001,26 +8001,26 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -8029,23 +8029,23 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>32500</v>
+        <v>175000</v>
       </c>
       <c r="L101" t="n">
         <v>100</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -8059,19 +8059,19 @@
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-05 09:44:21</t>
+          <t>2026-10-14 13:53:42</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -8079,26 +8079,26 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -8107,23 +8107,23 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>32500</v>
+        <v>100000</v>
       </c>
       <c r="L102" t="n">
         <v>100</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -8137,19 +8137,19 @@
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-06 10:07:08</t>
+          <t>2026-10-15 17:38:09</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8167,41 +8167,41 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>30</v>
+        <v>2578</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>750000</v>
+        <v>65000</v>
       </c>
       <c r="L103" t="n">
         <v>100</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -8215,19 +8215,19 @@
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:17</t>
+          <t>2026-10-15 17:38:09</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8245,41 +8245,41 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operational side consumption</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>30</v>
+        <v>1157</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>500000</v>
+        <v>33000</v>
       </c>
       <c r="L104" t="n">
         <v>100</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -8293,19 +8293,19 @@
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>31 Agustus 2026</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:17</t>
+          <t>2026-10-15 17:44:44</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8323,20 +8323,20 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>operational consumption</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>30</v>
+        <v>3195</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8350,14 +8350,14 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>500000</v>
+        <v>65000</v>
       </c>
       <c r="L105" t="n">
         <v>100</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-06 10:34:17</t>
+          <t>2026-10-15 17:44:44</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8401,20 +8401,20 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operational side consumption</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>30</v>
+        <v>1488</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>500000</v>
+        <v>33000</v>
       </c>
       <c r="L106" t="n">
         <v>100</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -8461,7 +8461,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -8469,51 +8469,51 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>750000</v>
+        <v>32500</v>
       </c>
       <c r="L107" t="n">
         <v>100</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -8527,7 +8527,7 @@
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -8547,51 +8547,51 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>750000</v>
+        <v>84500</v>
       </c>
       <c r="L108" t="n">
         <v>100</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -8605,7 +8605,7 @@
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -8617,7 +8617,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -8625,51 +8625,51 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>650000</v>
+        <v>26000</v>
       </c>
       <c r="L109" t="n">
         <v>100</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -8683,7 +8683,7 @@
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -8695,7 +8695,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -8703,51 +8703,51 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>650000</v>
+        <v>9750</v>
       </c>
       <c r="L110" t="n">
         <v>100</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -8761,7 +8761,7 @@
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -8773,7 +8773,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -8781,51 +8781,51 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>600000</v>
+        <v>19500</v>
       </c>
       <c r="L111" t="n">
         <v>100</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -8839,7 +8839,7 @@
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -8851,7 +8851,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-06 11:18:50</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -8859,51 +8859,51 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>600000</v>
+        <v>13000</v>
       </c>
       <c r="L112" t="n">
         <v>100</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -8917,7 +8917,7 @@
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -8929,7 +8929,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-06 11:41:07</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -8937,51 +8937,51 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>500000</v>
+        <v>9750</v>
       </c>
       <c r="L113" t="n">
         <v>100</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -9007,7 +9007,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33:47</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -9015,30 +9015,30 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -9048,18 +9048,18 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>11 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>250000</v>
+        <v>19500</v>
       </c>
       <c r="L114" t="n">
         <v>100</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr">
         <is>
-          <t>11 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-06 17:52:52</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -9093,51 +9093,51 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>458.4</v>
+        <v>48</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>25000</v>
+        <v>15600</v>
       </c>
       <c r="L115" t="n">
         <v>100</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -9151,7 +9151,7 @@
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -9163,7 +9163,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-06 18:51:53</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -9186,11 +9186,11 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>2188</v>
+        <v>10</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9199,23 +9199,23 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>7500</v>
+        <v>32500</v>
       </c>
       <c r="L116" t="n">
         <v>100</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -9229,19 +9229,19 @@
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-06 18:51:53</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9264,11 +9264,11 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9277,23 +9277,23 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>53300</v>
+        <v>32500</v>
       </c>
       <c r="L117" t="n">
         <v>100</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -9307,19 +9307,19 @@
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-06 19:04:22</t>
+          <t>2026-10-16 10:58:15</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -9327,51 +9327,51 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>60000000</v>
+        <v>32500</v>
       </c>
       <c r="L118" t="n">
         <v>100</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -9385,19 +9385,19 @@
       <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>03 September 2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -9405,51 +9405,51 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>25000000</v>
+        <v>32500</v>
       </c>
       <c r="L119" t="n">
         <v>100</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -9463,19 +9463,19 @@
       <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -9483,51 +9483,51 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>17500000</v>
+        <v>84500</v>
       </c>
       <c r="L120" t="n">
         <v>100</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Support Well Services Senoro Periode 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -9541,19 +9541,19 @@
       <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -9561,51 +9561,51 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>60000000</v>
+        <v>26000</v>
       </c>
       <c r="L121" t="n">
         <v>100</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Operasi Shift Siang Periode 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -9619,19 +9619,19 @@
       <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -9639,51 +9639,51 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>60000000</v>
+        <v>9750</v>
       </c>
       <c r="L122" t="n">
         <v>100</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -9697,19 +9697,19 @@
       <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -9717,51 +9717,51 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>15000000</v>
+        <v>19500</v>
       </c>
       <c r="L123" t="n">
         <v>100</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -9775,19 +9775,19 @@
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-07 06:11:16</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -9795,51 +9795,51 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>15000000</v>
+        <v>13000</v>
       </c>
       <c r="L124" t="n">
         <v>100</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Operasi Shift Malam Periode 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -9853,19 +9853,19 @@
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-07 08:41:55</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -9873,51 +9873,51 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>7500000</v>
+        <v>9750</v>
       </c>
       <c r="L125" t="n">
         <v>100</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -9931,19 +9931,19 @@
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-07 08:41:55</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -9951,51 +9951,51 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>7500000</v>
+        <v>19500</v>
       </c>
       <c r="L126" t="n">
         <v>100</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -10009,19 +10009,19 @@
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:04</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -10029,51 +10029,51 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>7600000</v>
+        <v>15600</v>
       </c>
       <c r="L127" t="n">
         <v>100</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -10087,19 +10087,19 @@
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:04</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -10107,51 +10107,51 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>7600000</v>
+        <v>32500</v>
       </c>
       <c r="L128" t="n">
         <v>100</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -10165,19 +10165,19 @@
       <c r="V128" t="inlineStr"/>
       <c r="W128" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -10185,51 +10185,51 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>5290000</v>
+        <v>32500</v>
       </c>
       <c r="L129" t="n">
         <v>100</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -10243,19 +10243,19 @@
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-16 11:08:08</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -10263,51 +10263,51 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>5290000</v>
+        <v>32500</v>
       </c>
       <c r="L130" t="n">
         <v>100</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -10321,19 +10321,19 @@
       <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -10341,51 +10341,51 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>6555000</v>
+        <v>32500</v>
       </c>
       <c r="L131" t="n">
         <v>100</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA muat equipment well services</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -10399,19 +10399,19 @@
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -10419,51 +10419,51 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>6555000</v>
+        <v>84500</v>
       </c>
       <c r="L132" t="n">
         <v>100</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -10477,19 +10477,19 @@
       <c r="V132" t="inlineStr"/>
       <c r="W132" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-07 09:32:22</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -10497,51 +10497,51 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>6555000</v>
+        <v>26000</v>
       </c>
       <c r="L133" t="n">
         <v>100</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -10555,19 +10555,19 @@
       <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -10575,51 +10575,51 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>5290000</v>
+        <v>9750</v>
       </c>
       <c r="L134" t="n">
         <v>100</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -10633,19 +10633,19 @@
       <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -10653,51 +10653,51 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K135" t="n">
-        <v>5290000</v>
+        <v>19500</v>
       </c>
       <c r="L135" t="n">
         <v>100</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -10711,19 +10711,19 @@
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -10731,51 +10731,51 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K136" t="n">
-        <v>6555000</v>
+        <v>13000</v>
       </c>
       <c r="L136" t="n">
         <v>100</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8950 RA muat Equipment Well Services</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -10789,19 +10789,19 @@
       <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -10809,51 +10809,51 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>7600000</v>
+        <v>9750</v>
       </c>
       <c r="L137" t="n">
         <v>100</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -10867,19 +10867,19 @@
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-07 10:41:03</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -10887,26 +10887,26 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -10915,23 +10915,23 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K138" t="n">
-        <v>7600000</v>
+        <v>19500</v>
       </c>
       <c r="L138" t="n">
         <v>100</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -10945,19 +10945,19 @@
       <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr">
         <is>
-          <t>20 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:18</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -10965,51 +10965,51 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>7600000</v>
+        <v>32500</v>
       </c>
       <c r="L139" t="n">
         <v>100</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -11023,19 +11023,19 @@
       <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:18</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -11043,51 +11043,51 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>23 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>7600000</v>
+        <v>32500</v>
       </c>
       <c r="L140" t="n">
         <v>100</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -11101,19 +11101,19 @@
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-07 11:27:18</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -11121,51 +11121,51 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>5520000</v>
+        <v>32500</v>
       </c>
       <c r="L141" t="n">
         <v>100</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -11179,19 +11179,19 @@
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr">
         <is>
-          <t>29 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:15</t>
+          <t>2026-10-16 11:10:36</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -11199,51 +11199,51 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>1600000</v>
+        <v>15600</v>
       </c>
       <c r="L142" t="n">
         <v>100</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -11257,19 +11257,19 @@
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:15</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -11277,51 +11277,51 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>1600000</v>
+        <v>32500</v>
       </c>
       <c r="L143" t="n">
         <v>100</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -11335,19 +11335,19 @@
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:15</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -11355,51 +11355,51 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>27 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>1600000</v>
+        <v>84500</v>
       </c>
       <c r="L144" t="n">
         <v>100</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -11413,19 +11413,19 @@
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:15</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -11433,51 +11433,51 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>1600000</v>
+        <v>26000</v>
       </c>
       <c r="L145" t="n">
         <v>100</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -11491,19 +11491,19 @@
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-10-10 08:57:15</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -11511,51 +11511,51 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K146" t="n">
-        <v>1600000</v>
+        <v>9750</v>
       </c>
       <c r="L146" t="n">
         <v>100</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -11569,19 +11569,19 @@
       <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-13 10:26:58</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -11589,51 +11589,51 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K147" t="n">
-        <v>1500000</v>
+        <v>19500</v>
       </c>
       <c r="L147" t="n">
         <v>100</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -11647,19 +11647,19 @@
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>14 Agustus 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-13 10:35:35</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -11667,51 +11667,51 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>7500000</v>
+        <v>13000</v>
       </c>
       <c r="L148" t="n">
         <v>100</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -11725,19 +11725,19 @@
       <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-14 13:23:53</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -11745,51 +11745,51 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>10000</v>
+        <v>9750</v>
       </c>
       <c r="L149" t="n">
         <v>100</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -11803,19 +11803,19 @@
       <c r="V149" t="inlineStr"/>
       <c r="W149" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-14 13:23:53</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -11823,51 +11823,51 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>15000</v>
+        <v>19500</v>
       </c>
       <c r="L150" t="n">
         <v>100</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -11881,19 +11881,19 @@
       <c r="V150" t="inlineStr"/>
       <c r="W150" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>30 Januari 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-14 13:53:42</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -11901,26 +11901,26 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -11929,23 +11929,23 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>175000</v>
+        <v>15600</v>
       </c>
       <c r="L151" t="n">
         <v>100</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -11959,19 +11959,19 @@
       <c r="V151" t="inlineStr"/>
       <c r="W151" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-10-14 13:53:42</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -11979,26 +11979,26 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -12007,23 +12007,23 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K152" t="n">
-        <v>100000</v>
+        <v>32500</v>
       </c>
       <c r="L152" t="n">
         <v>100</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -12037,19 +12037,19 @@
       <c r="V152" t="inlineStr"/>
       <c r="W152" t="inlineStr">
         <is>
-          <t>04 September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-10-15 17:38:09</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -12057,51 +12057,51 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>operational consumption</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>2578</v>
+        <v>10</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>65000</v>
+        <v>32500</v>
       </c>
       <c r="L153" t="n">
         <v>100</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -12115,19 +12115,19 @@
       <c r="V153" t="inlineStr"/>
       <c r="W153" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-10-15 17:38:09</t>
+          <t>2026-10-16 11:30:15</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -12135,51 +12135,51 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Operational side consumption</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1157</v>
+        <v>10</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>08 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K154" t="n">
-        <v>33000</v>
+        <v>32500</v>
       </c>
       <c r="L154" t="n">
         <v>100</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -12193,19 +12193,19 @@
       <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr">
         <is>
-          <t>31 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>03 Agustus 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-10-15 17:44:44</t>
+          <t>2026-10-16 11:48:40</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -12225,16 +12225,16 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>operational consumption</t>
+          <t>Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>3195</v>
+        <v>4</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -12243,23 +12243,23 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="K155" t="n">
-        <v>65000</v>
+        <v>7500000</v>
       </c>
       <c r="L155" t="n">
         <v>100</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Mobilisasi 2 Unit Lighting Tower dan 2 Unit Mesin Genset 80 KVA dari Luwuk ke Senoro Cluster B</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -12273,92 +12273,12 @@
       <c r="V155" t="inlineStr"/>
       <c r="W155" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>08 Agustus 2026</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>03 September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-10-15 17:44:44</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Operational side consumption</t>
-        </is>
-      </c>
-      <c r="G156" t="n">
-        <v>1488</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>01 September 2026</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="K156" t="n">
-        <v>33000</v>
-      </c>
-      <c r="L156" t="n">
-        <v>100</v>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>03 September 2026</t>
+          <t>03 Agustus 2026</t>
         </is>
       </c>
     </row>
